--- a/08_third-party-ai-model-risk-assessment/demo/vendor_governance_demo.xlsx
+++ b/08_third-party-ai-model-risk-assessment/demo/vendor_governance_demo.xlsx
@@ -621,7 +621,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -848,7 +847,7 @@
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>"Yes"
-Reasoning: Bedrock supports bias detection in foundation models</t>
+Reasoning: Bedrock Guardrails supports content-safety filtering — denied topics, contextual grounding, harmful-output detection, and PII redaction.</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -1298,7 +1297,7 @@
       <c r="H3" s="8" t="inlineStr">
         <is>
           <t>"Immediate notification per PCI DSS requirements"
-Reasoning: PCI DSS mandates breach notification within 72 hours; CloudFirst notifies customers within 24h</t>
+Reasoning: PCI DSS requires notification of acquirers / card brands without delay. The 72-hour figure is the GDPR Article 33 deadline for personal-data breach notification to the supervisory authority; CloudFirst commits to customer notification within 24h.</t>
         </is>
       </c>
     </row>
